--- a/out/policy_events_2026-05-07.xlsx
+++ b/out/policy_events_2026-05-07.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +471,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>美 ‘車관세 인상’ 발표에…마크롱 ‘무역 바주카포’ 보복 요구 - 동아일보</t>
+          <t>김정관 산업장관 "1호 대미 투자 6월 이후 … 관세 15% 넘지 않게 노력" - 뉴데일리 경제</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>美 ‘車관세 인상’ 발표에…마크롱 ‘무역 바주카포’ 보복 요구&amp;nbsp;&amp;nbsp;동아일보美,"EU의 협정 비준지연"비난…자동차 관세 25% 부과 가능성 높아져&amp;nbsp;&amp;nbsp;v.daum.netEU, 트럼프 車관세 인상 위협에 "약속은 약속…합의 지켜라"&amp;nbsp;&amp;nbsp;뉴시스</t>
+          <t>김정관 산업장관 "1호 대미 투자 6월 이후 … 관세 15% 넘지 않게 노력"&amp;nbsp;&amp;nbsp;뉴데일리 경제</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 08:19:00 GMT</t>
+          <t>Wed, 06 May 2026 22:47:30 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9WNTViTmhZUEtZMDZTQ1VDbVJtaUhIUGhDNkNzSHVRWUJTT3V1MHl1Z05UN2NUV2h4V0xmZ1lHbU0wM1Fid2JlMTVRQVA2UnlhNDlPRUtzVGN2QXp5a2V0RG8tdUpCck1YZy1KUTZSRjNvY0HSAWZBVV95cUxPWm9Nd2RGMGN6MzZKV25QRmdCRHVELXI3OHRNR2NnMXBpYmVYaTMweGNUTFhYbHJsNzBMWjhmSGtWSnZBRHBwNmI4OHMxY2dqaW9YekE5ZXV5MTFRNkM2SHlCdldmYkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE5YNXdYVzRiV3NyNmJCZlN4ZlI2WFVTTkdyVTFhQVgtZGk4TXI4bmplLTYwRzNvb1VuNGFGdWhqb1RUcWk5aGM5Yk5mTXNGY1ZoUTdmemdxVExJUUkzRjJ1bTk2VVhNeTduUFVPWDRnWUZSb0dzUWdpRDJrTQ?oc=5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -508,32 +508,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>공급망 '흔들' 관세 손실 '눈덩이'…글로벌 완성차 위기감 고조 - 지디넷코리아</t>
+          <t>산업장관 "첫 대미투자, 6월 법 시행후…新관세 15% 안넘게 노력"(종합) - 연합뉴스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>공급망 '흔들' 관세 손실 '눈덩이'…글로벌 완성차 위기감 고조&amp;nbsp;&amp;nbsp;지디넷코리아</t>
+          <t>산업장관 "첫 대미투자, 6월 법 시행후…新관세 15% 안넘게 노력"(종합)&amp;nbsp;&amp;nbsp;연합뉴스</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 07:46:32 GMT</t>
+          <t>Wed, 06 May 2026 22:06:06 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5YcTZ0LVQ3cktvZ0dqUVpaZ2U1YjlUTUZsUEU1ZUVRQ1Q2NjhNNHkxVWo4OVdBVGpEQUMzQmtFdHlWWW8zVUdlWnNvRm5ydFpFLWtQVEdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE40V3FqYm5Uc3ZwSHd4cTVJMVNtQ0FvOXFVOWlwcHFBYndwdUVoRHlDN0Z0Y1ZoeG9KVUJjTFJsci1lR1RuX1VLN0s0TnAwTFlvYnhBOFdfNnRaUDDSAWBBVV95cUxQc1NJcThkRF9WUVpUVHhuOFAyekFOY0lnY1cyZ3NYMjhFbURXLXdRTjZmbmdORmxBM0VDY2pUNzlOVXhVY3BsRHBFVTUzcmtqcDNyVm0yVmpMenVOWGxnVHE?oc=5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -545,22 +545,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>무역협회, 美관세 대응 온라인 설명회…"환급 신청 서둘러야" - 뉴시스</t>
+          <t>산업장관 "첫 대미투자, 6월 이후…새 관세 15% 안 넘게 노력" - SBS 뉴스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>무역협회, 美관세 대응 온라인 설명회…"환급 신청 서둘러야"&amp;nbsp;&amp;nbsp;뉴시스</t>
+          <t>산업장관 "첫 대미투자, 6월 이후…새 관세 15% 안 넘게 노력"&amp;nbsp;&amp;nbsp;SBS 뉴스</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 06:58:18 GMT</t>
+          <t>Wed, 06 May 2026 23:43:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBCc2tWaFdDU1R4dGtoZmYtTEt4N2dSLTlZUzhwd0J4TkswSE5Vc3VSVnFKZG1EZnpMSnN3M09YRGZ6SE9rSkJyaVlVeDNhU05wQlZRSFJBQlVkb3Q4dVFtdNIBeEFVX3lxTE9KaFQ2ODFpY2EyRTR2RlA1N1ZKV3lTbTRINkVKcVhlN1RlU2Exa1g2N1ZQWlhEYmxyVTlpNXh1dV9FUWdxYjhGbG90NkozUW5TX3JsalBoOUg5bDVGR0JQSVF5YXpZb29fNjY5S2kyaFgxZkJPWUI4Zg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBFQThIdXpRVk5McERGZHh4VXZTOTduYkNrS0ludHRrTFE4Yk4yQnBFMmdHYkJ4LVpyek4tV1ZNWG12UnU0WDhabmYzbnd4M0M1bmY4TEhkOXdCQ3N3WkZ0SEk3MXktYWwwQWc?oc=5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -582,22 +582,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>무협, 미국 관세환급 온라인 설명회…"신청 서둘러야" - 매일경제 마켓</t>
+          <t>'위법' 트럼프 관세, 수입업체 계좌에 환급금 입금 시작 - 마켓인</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>무협, 미국 관세환급 온라인 설명회…"신청 서둘러야"&amp;nbsp;&amp;nbsp;매일경제 마켓</t>
+          <t>'위법' 트럼프 관세, 수입업체 계좌에 환급금 입금 시작&amp;nbsp;&amp;nbsp;마켓인</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 08:07:31 GMT</t>
+          <t>Wed, 06 May 2026 21:55:15 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5iQVRsd2Y3enRmTHlRYWVTVTA5R2xUODFwdVpnbC04SzRZdGhWX1djbjNCMWlwV1I3S2Q3NERNTGJiU2U3SGVXcmt1SmhzSjNxa3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBQbURHei1QRGFZSklGZzUxeTMzV1g0Qk9JZlh2X05OczZDQzNORnlKNHJ6MV9TYjlScldLVUR0aUZweW5xZUh3NmhYZ054OUEyVGZWajN1UFhtb0xJdXR3OGhSbDBXbUEzcVhMdnJHMG02cGM?oc=5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -619,32 +619,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>"美 관세 환급 서둘러야"…원산지 오류 땐 추징·과징금 역풍 주의 - 뉴스1</t>
+          <t>무역협회, 美관세 대응 온라인 설명회…"환급 신청 서둘러야" - 뉴시스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>"美 관세 환급 서둘러야"…원산지 오류 땐 추징·과징금 역풍 주의&amp;nbsp;&amp;nbsp;뉴스1</t>
+          <t>무역협회, 美관세 대응 온라인 설명회…"환급 신청 서둘러야"&amp;nbsp;&amp;nbsp;뉴시스무협, 미국 관세환급 온라인 설명회…"신청 서둘러야"&amp;nbsp;&amp;nbsp;매일경제 마켓"1660억달러 환급 지연"…월가, 기업 ‘관세 돈줄’ 사들이는 이유 [글로벌 머니 X파일]&amp;nbsp;&amp;nbsp;한국경제</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 06:44:47 GMT</t>
+          <t>Wed, 06 May 2026 06:58:18 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzUnRKY1J5NmRkT05WYnVPa0RxU1BPSmFRYURqVU1pSHgtUC1JVFFqbmpuQ3o1cHJjeWRCRW8yRG12c0FFWTllZjctXzFkZkUyWmFYZnhOTl9QbzhpdExuQm9oX1I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBCc2tWaFdDU1R4dGtoZmYtTEt4N2dSLTlZUzhwd0J4TkswSE5Vc3VSVnFKZG1EZnpMSnN3M09YRGZ6SE9rSkJyaVlVeDNhU05wQlZRSFJBQlVkb3Q4dVFtdNIBeEFVX3lxTE9KaFQ2ODFpY2EyRTR2RlA1N1ZKV3lTbTRINkVKcVhlN1RlU2Exa1g2N1ZQWlhEYmxyVTlpNXh1dV9FUWdxYjhGbG90NkozUW5TX3JsalBoOUg5bDVGR0JQSVF5YXpZb29fNjY5S2kyaFgxZkJPWUI4Zg?oc=5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -656,22 +656,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'전쟁 여파' 중동 우회 선박 관세부담 덜어준다…국무회의 의결 - 연합뉴스</t>
+          <t>반도체와 '원투펀치' 자동차 수출 주춤…美관세·유가 직격탄 - 뉴시스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'전쟁 여파' 중동 우회 선박 관세부담 덜어준다…국무회의 의결&amp;nbsp;&amp;nbsp;연합뉴스</t>
+          <t>반도체와 '원투펀치' 자동차 수출 주춤…美관세·유가 직격탄&amp;nbsp;&amp;nbsp;뉴시스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 04:55:57 GMT</t>
+          <t>Wed, 06 May 2026 20:00:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE80eHF2ZVJIc3RvY0hvX1ktMUNreXdTdlEzMlI0RHBEUU9BQ0Jabk9BWWFDVENyQ2pweW1ZRlB3X3plYUJmcmh1T0dWY0U5YWZXQnhodV9XLTJrZUnSAWBBVV95cUxQSW1lYldpaWlZdV9XTTFxWVFhYnR2Um9ZSW52ZFdEZDk5N2JZblc0cXpjVnpVbFNSSTBtMTdNUzBqQm1tT2YteWJCaFI3NU0xQW82QUFjMXVSalhBb1pSSV8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBUaUFMZ01hOHB0RWZWWWl1SS1BWUdtMDdlWWZjOEk4SGg0NnZMakdTdmxLSUJ1N3Q3SnVNVXVGQ2pwTEV2QnRDd2tiNkhRYWJMTERQNFFtOEl0UE5WQUNuZtIBeEFVX3lxTFB4bWZlRDlKTlowXzRwT2NpNkpUYjFPS3ozMGdiM0JmR2lMSE5jS2VPX3EzdEJQNW9VNm9QVGJRUENHcXIwV1FoM2VnSkxjNXlXcG9lY2JRa3NTaW1tdnV2blBGeTN3QnhTTllEWGZHMnRkNHJYaEpuYQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>경기도, ‘수출기업 지원’ 2246억원 규모 펀드 조성···“대미 관세·중동 정세 불안 대응” - 경향신문</t>
+          <t>공급망 '흔들' 관세 손실 '눈덩이'…글로벌 완성차 위기감 고조 - 지디넷코리아</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>경기도, ‘수출기업 지원’ 2246억원 규모 펀드 조성···“대미 관세·중동 정세 불안 대응”&amp;nbsp;&amp;nbsp;경향신문</t>
+          <t>공급망 '흔들' 관세 손실 '눈덩이'…글로벌 완성차 위기감 고조&amp;nbsp;&amp;nbsp;지디넷코리아</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 01:32:00 GMT</t>
+          <t>Wed, 06 May 2026 07:46:32 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE11elZudEFVYmtqc3h0M3NiRVBIdDctZExSeGJCT1Myck52dTBDdmlqcmRmQ2hSVjljdkJFQzBvQldnUWpBQUVVQTZ0NnpNZU1GUE9TWGQzSHV3d9IBX0FVX3lxTE5BOTVmUkxKR2RHOUc3TlJncHFKdDVmNXFidjAtMHN6N3F1QklIbTJQMFlvZjI1YjM4ai1fTkpBeG9iWmFhbk5SdkdQR2VCODhzOHM1OE44T2Z1bGNRXzJF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5YcTZ0LVQ3cktvZ0dqUVpaZ2U1YjlUTUZsUEU1ZUVRQ1Q2NjhNNHkxVWo4OVdBVGpEQUMzQmtFdHlWWW8zVUdlWnNvRm5ydFpFLWtQVEdB?oc=5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -730,22 +730,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>현대百 본업 성과 가린 자회사 지누스…올해 관세 환급 변수 - 연합인포맥스</t>
+          <t>EU “관세 위협 美, 협정 지켜라” 마크롱 “무역 바주카포 쓰자” - 동아일보</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>현대百 본업 성과 가린 자회사 지누스…올해 관세 환급 변수&amp;nbsp;&amp;nbsp;연합인포맥스</t>
+          <t>EU “관세 위협 美, 협정 지켜라” 마크롱 “무역 바주카포 쓰자”&amp;nbsp;&amp;nbsp;동아일보EU, 트럼프 車관세 인상 위협에 "약속은 약속…합의 지켜라"&amp;nbsp;&amp;nbsp;뉴시스美,"EU의 협정 비준지연"비난…자동차 관세 25% 부과 가능성 높아져&amp;nbsp;&amp;nbsp;한국경제</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 06:01:50 GMT</t>
+          <t>Wed, 06 May 2026 19:30:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBjNVYtelBWSndyeXdqM3F6bjN1N3daRE5UZEFNV2g3T01SemFUclVpa3YyVElIR2JyY1owRTZOSWxJU0IwYkU0ckdWUE91NFk5Q0l1R00zVUljS1VTbmRJNi1nZW9IQnpVTmxWSmNsYTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9XMmJZb0RIcXFycnNwWVZjTThDTjE0b2ZCWk5sZDFOZ1B1YmJ5MF9ERTRrQ3RpQ2JzTW9GZEFNNVhtUERhRmg4VDNCUFRsVFVCakNrclBGZUNRN0ZHZVJCX0hTeUozMUkwekNBSjBvZEZaVUXSAWZBVV95cUxNeEJSOVNNNUl3dG1OQXhWUTFwQkJBU0xWTXQxLUV1YWdrSnZoY1JPZnc5cFZ3bUVZYnRjOFdwcndpT3hubjRMQnZfQ3lETGgyLXNhQ0VyQUJqdk5GU1NmSTBqMC1Jb2c?oc=5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -767,22 +767,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>‘미군 철수·車 관세’ 직면 獨총리 “美, 변함없이 가장 중요한 파트너”…사태 수습 나서 - 문화일보</t>
+          <t>중동 우회 선박 관세부담 완화한다...국무회의 의결 - YTN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>‘미군 철수·車 관세’ 직면 獨총리 “美, 변함없이 가장 중요한 파트너”…사태 수습 나서&amp;nbsp;&amp;nbsp;문화일보</t>
+          <t>중동 우회 선박 관세부담 완화한다...국무회의 의결&amp;nbsp;&amp;nbsp;YTN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 06:42:19 GMT</t>
+          <t>Wed, 06 May 2026 20:53:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE04bDF4N1hnM2lqLTd3M1lqRG5UYmJoY1VhcTNFeEd2NHpCRVdRV0J5cGI1NXBoc3JNMm56MWhWbEU4WHQtTVpCb0hveTFMVmJq?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBIcTk3WWhxUUh2akFhZDFndlNOUy0xNkpEejdQWFR2bFVOc1RYblpkWXl2ZVJPUmlXTWdJeWFFQTRTUmc2dHozN1VCVzlJOXA1Zk5rbnM2Um1sUlIycWc?oc=5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -804,22 +804,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>美, 대체관세 사전작업 ‘301조 공청회’ 실시…韓 “과잉생산 품목 자발적 구조조정” 해명 - 헤럴드경제</t>
+          <t>우회 선박 ‘통상 운임’ 관세 적용…전세사기 보증금 ‘3분의 1’ 국가가 보장 - v.daum.net</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>美, 대체관세 사전작업 ‘301조 공청회’ 실시…韓 “과잉생산 품목 자발적 구조조정” 해명&amp;nbsp;&amp;nbsp;헤럴드경제</t>
+          <t>우회 선박 ‘통상 운임’ 관세 적용…전세사기 보증금 ‘3분의 1’ 국가가 보장&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 21:10:20 GMT</t>
+          <t>Wed, 06 May 2026 05:15:02 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1WTWdmUkdZbXh2WnFwc1ZfR0M2ZkY4dVpQcS1LaHpkZnd1VHBnTWhMMS1WNm9ZRFQzT0FwMDRjWlA2Ym5kWjhBVXZlM3VHckRBS1AteWJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5vOEMydUw5c0FxQU9zVkRhbDhkY0RNRTJPLVJXM19QU2V4aWc1OGhKRTZJMDZ1RzNuOFF5dFFFMGp3SHRqQW1reHVKMXhZWk0?oc=5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -841,22 +841,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>트럼프, 301조로 관세 재시동…대내외 충돌 커진다 - v.daum.net</t>
+          <t>'중동 전쟁' 여파, 우회 선박 관세 부담 감면…국무회의 통과 - 뉴스핌</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>트럼프, 301조로 관세 재시동…대내외 충돌 커진다&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>'중동 전쟁' 여파, 우회 선박 관세 부담 감면…국무회의 통과&amp;nbsp;&amp;nbsp;뉴스핌</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 01:52:51 GMT</t>
+          <t>Wed, 06 May 2026 06:27:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE95WnFDVVU5bXBIX3NmajhfUWFUOGlTeUpvckN1SDEzeDBaU0g3WWlKZXVEN251OUtQUFE3QzF0OEdweWkzMUI2bWdDTXc1d0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE15QV85Z0kxeGY4LUpUb1ExbHgtTENoNTNQMVRIVjFkS05taUUzTFMtN2FCS1BkbXNTSnU3cTNVaEJZUlRVdlYzX2daUjBWUmNvaE03M3paOTg3MmJV?oc=5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -878,22 +878,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>정부, 美USTR '301조 공청회'서 "시장원칙·한미협력" 강조 - 연합뉴스</t>
+          <t>경기도, ‘수출기업 지원’ 2246억원 규모 펀드 조성···“대미 관세·중동 정세 불안 대응” - 경향신문</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>정부, 美USTR '301조 공청회'서 "시장원칙·한미협력" 강조&amp;nbsp;&amp;nbsp;연합뉴스</t>
+          <t>경기도, ‘수출기업 지원’ 2246억원 규모 펀드 조성···“대미 관세·중동 정세 불안 대응”&amp;nbsp;&amp;nbsp;경향신문</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 19:38:10 GMT</t>
+          <t>Wed, 06 May 2026 01:32:00 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1KaVBwN3pZblhWT1g2ZGlsRDJzbG56T3BWV2tjMFVOcXdFcGFWZVE3eVFzUVE4cVYydVFGMk9fR3hnQThuMDAyU1NpOWhzeFFXSUZFcWU3dkZKSTjSAWBBVV95cUxNTmxHTFZTRGpkWk5RWTc4c1hiWUJ0dk9VdmpXUWdVZ1d5S1czSUpCakdMTWRzakw4QWFMMzNUNFFCTjVEMTBKN2gxM2k3MUJKZzcwdmJzd0NNMWpvRmdva0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE11elZudEFVYmtqc3h0M3NiRVBIdDctZExSeGJCT1Myck52dTBDdmlqcmRmQ2hSVjljdkJFQzBvQldnUWpBQUVVQTZ0NnpNZU1GUE9TWGQzSHV3d9IBX0FVX3lxTE5BOTVmUkxKR2RHOUc3TlJncHFKdDVmNXFidjAtMHN6N3F1QklIbTJQMFlvZjI1YjM4ai1fTkpBeG9iWmFhbk5SdkdQR2VCODhzOHM1OE44T2Z1bGNRXzJF?oc=5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -915,22 +915,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>파병 안 하면 관세 25%? … 트럼프, 중동 리스크를 '통상 보복' 지렛대 삼나 - 뉴데일리 경제</t>
+          <t>현대百 본업 성과 가린 자회사 지누스…올해 관세 환급 변수 - 연합인포맥스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>파병 안 하면 관세 25%? … 트럼프, 중동 리스크를 '통상 보복' 지렛대 삼나&amp;nbsp;&amp;nbsp;뉴데일리 경제</t>
+          <t>현대百 본업 성과 가린 자회사 지누스…올해 관세 환급 변수&amp;nbsp;&amp;nbsp;연합인포맥스</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 01:18:20 GMT</t>
+          <t>Wed, 06 May 2026 06:01:50 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBxYXk2UWdXT0pVajJJcnI4V3hhcXFtel9WdFhQTHVpZGdhX2hEdmptcC1yRzRYN3RIcTVxWXdfVVBCVF85cnl5ZVlvOHQzQzFrTjQ4SUZXeGZkN2VuZy1tTFdYTlVET29QQzBZcHlNOVZlOUlNUnJncUxCMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBjNVYtelBWSndyeXdqM3F6bjN1N3daRE5UZEFNV2g3T01SemFUclVpa3YyVElIR2JyY1owRTZOSWxJU0IwYkU0ckdWUE91NFk5Q0l1R00zVUljS1VTbmRJNi1nZW9IQnpVTmxWSmNsYTA?oc=5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -952,22 +952,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>포트메이리온 그룹, 美 관세 여파로 720만 파운드 손실 기록 - Investing.com 한국어</t>
+          <t>[이슈] 美 USTR, 새로운 관세 부과 위한 '301조 공청회'…7월 관세 발표 전망 - 폴리뉴스 Polinews</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>포트메이리온 그룹, 美 관세 여파로 720만 파운드 손실 기록&amp;nbsp;&amp;nbsp;Investing.com 한국어</t>
+          <t>[이슈] 美 USTR, 새로운 관세 부과 위한 '301조 공청회'…7월 관세 발표 전망&amp;nbsp;&amp;nbsp;폴리뉴스 Polinews</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 06:17:00 GMT</t>
+          <t>Wed, 06 May 2026 05:51:03 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE00dGQzRHNVMFVVWF94WDc2TEtMQldDRFc4T1MwaVkwM1F6SFVIM29HZXVFb3p6RE1yWUhERUpZSjl0M016YURuYzJDMFZjZXBycmJ0SG1aTGUzMGpYZHA2eFZIUTg4U1czTWZ4Tmx0Q2E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE54U3d1V0lPbE9UXzU1ZEx2RTFqS0FMTHZPX0VNaWh5NURaOEhvWWRLSkVnNUVHYmRoQ2E2WGJCZklkSTB4a0VRU1FtMmx4a2JoVVFsRlozOFd6RUFzU2FTYVNwZ1pjQjNyVlA4Nmpn0gFyQVVfeXFMUFdFaUdvaGRRUHUtdmcwTUJEZF9YY3B5MFhBWkFsZUR5VnpyZXRwblprdlpFcTZEcldwdGVxMmdxM3cwdWpTX1VXUktkQVpmZ2VnaXpPbU9CR2Zia3VIaFdXM094UEN4VEQ1NGRrbEp3MnhR?oc=5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -989,22 +989,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>트럼프 ‘관세 폭탄’ vs EU ‘무역 바주카포’…대서양 무역전쟁 2라운드 초읽기 - JTBC</t>
+          <t>트럼프, 301조로 관세 재시동…대내외 충돌 커진다 - v.daum.net</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>트럼프 ‘관세 폭탄’ vs EU ‘무역 바주카포’…대서양 무역전쟁 2라운드 초읽기&amp;nbsp;&amp;nbsp;JTBC</t>
+          <t>트럼프, 301조로 관세 재시동…대내외 충돌 커진다&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 06:47:00 GMT</t>
+          <t>Wed, 06 May 2026 01:52:51 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9lN1RVQXdsVElwVTQ4dFdUclFkMWt1UUp3cG9yUVBNZmRONlVFU0F2UUtwakVRUUFIQTcyNXpTamQ2eEdWZG5IYzRSbmtLYWVIVHpfaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE95WnFDVVU5bXBIX3NmajhfUWFUOGlTeUpvckN1SDEzeDBaU0g3WWlKZXVEN251OUtQUFE3QzF0OEdweWkzMUI2bWdDTXc1d0E?oc=5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>관세 변수에도 간다…현대차그룹, 멕시코에 7억달러 베팅 - v.daum.net</t>
+          <t>방미 김정관 “대미 ‘1호 투자’ 6월 발표…관세 15% 안 넘게 노력” - 중앙일보</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>관세 변수에도 간다…현대차그룹, 멕시코에 7억달러 베팅&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>방미 김정관 “대미 ‘1호 투자’ 6월 발표…관세 15% 안 넘게 노력”&amp;nbsp;&amp;nbsp;중앙일보</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 09:59:33 GMT</t>
+          <t>Wed, 06 May 2026 22:50:11 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5kaTdoVDJ4Y1RHT1RhNnBuMlY0cDZfdDd1X1Y0YWwtTy1ESDRsRFJ6ZlVaRHlvNnp0THA0cEVkV2xWUEZsT1hlZV82QkhFVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1Pazd6X1FDSS1ESlVDTms1UWtKNnpxVnVrVlktU3dIQlNNanBuSW5kWkNESXFDWUp4OUFWTHBJbkZWNmpBRTFjeUl5aXgtSV9WWmRzM2ZR?oc=5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -1063,22 +1063,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>트럼프, 유럽차 관세 재인상…반사효과 주목 - 뉴스토마토</t>
+          <t>미, EU 자동차 관세 25%로 기습 인상… 럭셔리 카 시장 ‘직격탄’ - 글로벌이코노믹</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>트럼프, 유럽차 관세 재인상…반사효과 주목&amp;nbsp;&amp;nbsp;뉴스토마토</t>
+          <t>미, EU 자동차 관세 25%로 기습 인상… 럭셔리 카 시장 ‘직격탄’&amp;nbsp;&amp;nbsp;글로벌이코노믹</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 03:09:44 GMT</t>
+          <t>Wed, 06 May 2026 19:20:00 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBtd1JVRjRhZFowLVJrMDJBMzZGQVp3c3hQcWJldUFFSmxSRXVoVVFZTGZiS2dDNnYwc2pLUUNNTkZhblJUTzdDTjF2UjdJRHJUSlg4OVptelp6bWhZejRkcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQbDRPUUJfX192dEE2WnlGZ3BUVFlKTkJRU05UWlBidC1Uc1dKRjRpZTl3cXJFTzc0VGVCVDcxcmhmazEzMjByanJpWnFrdFNNMTEyZjBjN2dYak9MYnFhREFpaGJWNEYxS3Y5VVdrZUdzaW40SEh0UFR0NlFYamVIbGNMYm1zamp0?oc=5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1100,32 +1100,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>반복되는 관세 연장, 항공산업의 해법이 될 수 없다 - 톱데일리</t>
+          <t>관세 장벽을 넘는 마스터키, 원산지 증명과 리스크 관리 - 중소기업신문</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>반복되는 관세 연장, 항공산업의 해법이 될 수 없다&amp;nbsp;&amp;nbsp;톱데일리</t>
+          <t>관세 장벽을 넘는 마스터키, 원산지 증명과 리스크 관리&amp;nbsp;&amp;nbsp;중소기업신문</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 00:53:00 GMT</t>
+          <t>Wed, 06 May 2026 23:32:59 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFB0ZUNFRXdiY3dNeFhvLTZXcG9KZ0xBYUFaazB1aklMMmZMajZXTWN1NEdpVTJMRUs5RGwtbEtuM2RGR3VFVTJxaVZXSE9Tcmt6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBKbVVkV29aVVV4Y3dHRmxrVF93VlNTbGxPSHFtNGRZR2VzUDNsbkxtdWs0Y3h2d1NudktWZ3I3TEdOS3c4Wms5eUo5ckNvTXVhakxvMW1qUFRkeVBTT2lkcjI4aHBLMi1VT1lwdQ?oc=5</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I19" t="inlineStr"/>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>"美 정부 관세 환급, 표기 오류 발견시 과징금 이어질 수 있어" - 서울파이낸스</t>
+          <t>산업장관 “첫 대미 투자 발표는 6월 이후...관세 15% 안 넘게 노력” - v.daum.net</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>"美 정부 관세 환급, 표기 오류 발견시 과징금 이어질 수 있어"&amp;nbsp;&amp;nbsp;서울파이낸스</t>
+          <t>산업장관 “첫 대미 투자 발표는 6월 이후...관세 15% 안 넘게 노력”&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 06:55:49 GMT</t>
+          <t>Wed, 06 May 2026 22:58:03 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1JUlNOUGE1cVBCUHZqaUQ2YUpDbFBCUG8wRWt6Q3otcTR2NlFvYU9iUFNHb0htMXlUaGJScE5OTkVRbHlIUkhseTBXek11MWdUMm1iZGluWGJydk9Eb0hJQk9pQjNNU0dBdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE11cEw1YUszSG9uQ3ZIQ0gtUS1SNlktd0RGZ2hvbVhISWZGWkRxT1RVXzlJU2VtMklnb3Q1bVZWcmwwRzdKVFZFMDZnOU16LVU?oc=5</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1174,22 +1174,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>대미 수출 철강제품, 품목관세 0~50% 단계별 부과 … 한-미 품목번호 연계표 확인하세요 - 쉬핑뉴스넷</t>
+          <t>"트럼프, 관세 항소 가능성 있어…환급 신청 서둘러야" - 아시아경제</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>대미 수출 철강제품, 품목관세 0~50% 단계별 부과 … 한-미 품목번호 연계표 확인하세요&amp;nbsp;&amp;nbsp;쉬핑뉴스넷</t>
+          <t>"트럼프, 관세 항소 가능성 있어…환급 신청 서둘러야"&amp;nbsp;&amp;nbsp;아시아경제</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 01:07:50 GMT</t>
+          <t>Wed, 06 May 2026 06:57:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1xRTFjRG91dngzZDBBdUExYjVPZ1ZDek1pVGIyM1dYREF0aFFMSUVIYVVRdnRSaXp0Z0VuYlA0UlNiUDVTeWpFNUJZWExuRmJQSlpXaHFXTGNHb0VfS2J6QWNIeFFjbHNQdEJaZzhuWDBVaU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE1wWGxXQmpub0hNd1BrbjJaSXZ2Um9UbV8xUDZTUXNXamNRVlNKRm1hV2U5eHF3dnl5cWJVZDJBZHJZSjh5aFpJOUhIc3M0UVlmb1dLd0hyd0I4RVZjd1BWYzVn?oc=5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1211,22 +1211,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>"트럼프, 관세 항소 가능성 있어…환급 신청 서둘러야" - 아시아경제</t>
+          <t>트럼프 ‘관세 폭탄’ vs EU ‘무역 바주카포’…대서양 무역전쟁 2라운드 초읽기 - JTBC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>"트럼프, 관세 항소 가능성 있어…환급 신청 서둘러야"&amp;nbsp;&amp;nbsp;아시아경제</t>
+          <t>트럼프 ‘관세 폭탄’ vs EU ‘무역 바주카포’…대서양 무역전쟁 2라운드 초읽기&amp;nbsp;&amp;nbsp;JTBC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 06:57:52 GMT</t>
+          <t>Wed, 06 May 2026 06:47:00 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFB2WkxiNTBURDhUWUlGdWw3YnAtdWNNZjQwQUtoUXMwejcyRlhUaUtUSy1sc1NzTC1pRDM0Q3FQYTZKRUFJWnZQaGRFNUhTTXp2cllMRTQtMi1hRlZndHUwTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9lN1RVQXdsVElwVTQ4dFdUclFkMWt1UUp3cG9yUVBNZmRONlVFU0F2UUtwakVRUUFIQTcyNXpTamQ2eEdWZG5IYzRSbmtLYWVIVHpfaw?oc=5</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1248,22 +1248,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[이슈] 美 USTR, 새로운 관세 부과 위한 '301조 공청회'…7월 관세 발표 전망 - 폴리뉴스 Polinews</t>
+          <t>무협, 美 관세 환급 설명회 개최...“신청 서둘러야” - 서울경제</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[이슈] 美 USTR, 새로운 관세 부과 위한 '301조 공청회'…7월 관세 발표 전망&amp;nbsp;&amp;nbsp;폴리뉴스 Polinews</t>
+          <t>무협, 美 관세 환급 설명회 개최...“신청 서둘러야”&amp;nbsp;&amp;nbsp;서울경제</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 05:51:03 GMT</t>
+          <t>Wed, 06 May 2026 21:30:00 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE54U3d1V0lPbE9UXzU1ZEx2RTFqS0FMTHZPX0VNaWh5NURaOEhvWWRLSkVnNUVHYmRoQ2E2WGJCZklkSTB4a0VRU1FtMmx4a2JoVVFsRlozOFd6RUFzU2FTYVNwZ1pjQjNyVlA4Nmpn0gFyQVVfeXFMUFdFaUdvaGRRUHUtdmcwTUJEZF9YY3B5MFhBWkFsZUR5VnpyZXRwblprdlpFcTZEcldwdGVxMmdxM3cwdWpTX1VXUktkQVpmZ2VnaXpPbU9CR2Zia3VIaFdXM094UEN4VEQ1NGRrbEp3MnhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTFBBM0xCUVV6VTFUckt1YXpDaFFhd0xmaXI2MV9EMXduVlR4ZmtWVFVMbURuN09RMWdOa1BDcElQXzZESTF2QWM2ZndfeG1WOVpJQlHSAVNBVV95cUxNZnpfeF9pa2Rac3pwZnRKWmRZbHFrYktwMjVlb0VGRWVTdllQR3BTaUM3OXh6Q2hycnNCbG9vMzVHQndQT1ZYZjJBMGJKZjVPUlo4RQ?oc=5</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>무협, 대미 수출기업 대상 상호관세 환급 설명회 개최 - 아이뉴스24</t>
+          <t>산업장관 "첫 대미투자, 6월 법 시행 후‥새로운 관세 15% 안 넘게 노력" - v.daum.net</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>무협, 대미 수출기업 대상 상호관세 환급 설명회 개최&amp;nbsp;&amp;nbsp;아이뉴스24</t>
+          <t>산업장관 "첫 대미투자, 6월 법 시행 후‥새로운 관세 15% 안 넘게 노력"&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 08:26:06 GMT</t>
+          <t>Wed, 06 May 2026 23:37:12 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiTEFVX3lxTE9zMmxFeXlHd25zc1p6MEF6VW5KWThFc0FPLUNNTWZWQnVRdEV3bGduVE9rM1FHTlNmd2JIZ1pKV29BUmI1RFN6M0JzTGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBqU1ZwUGl2WHBmZko4am9fWF9xckRpUDlWeENJdEVhQTl4S1hrQV9CeFdnRExFMUlqd0NPcnRrbGdzV2NrVnJzVGJUSlBRTDA?oc=5</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I24" t="inlineStr"/>
     </row>
@@ -1359,22 +1359,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>트럼프 관세 위협에 EU "합의 지켜라"…보복조치 경고 - v.daum.net</t>
+          <t>관세 변수에도 간다…현대차그룹, 멕시코에 7억달러 베팅 - v.daum.net</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>트럼프 관세 위협에 EU "합의 지켜라"…보복조치 경고&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>관세 변수에도 간다…현대차그룹, 멕시코에 7억달러 베팅&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 23:00:06 GMT</t>
+          <t>Wed, 06 May 2026 09:59:33 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE95c09CVW1FV19NQUFoUGJtZ2N1MTNpOXJ2X0dCQXFOUXNLUEQ2am1QNml6R3BHanF5dzVzUVZ4c19xdnNtWXBXU3ZDZkxlSEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5kaTdoVDJ4Y1RHT1RhNnBuMlY0cDZfdDd1X1Y0YWwtTy1ESDRsRFJ6ZlVaRHlvNnp0THA0cEVkV2xWUEZsT1hlZV82QkhFVWc?oc=5</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" t="inlineStr"/>
     </row>
@@ -1396,22 +1396,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>“환급 노리고 신고 오류 땐 역풍”…무협, 對美 관세 리스크 점검 - v.daum.net</t>
+          <t>'전쟁 여파' 중동 우회 선박 관세부담 덜어준다…국무회의 의결 - 연합뉴스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>“환급 노리고 신고 오류 땐 역풍”…무협, 對美 관세 리스크 점검&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>'전쟁 여파' 중동 우회 선박 관세부담 덜어준다…국무회의 의결&amp;nbsp;&amp;nbsp;연합뉴스</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 06:21:06 GMT</t>
+          <t>Wed, 06 May 2026 04:55:57 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1GS2ZFRkEwcHhCbWNNdktGZmNzM2tTYmdqcGFFZy1XWHJySUFONmtCYWlfLUg4SlV3NlBvTEE1dEs1X0VyNGtndV9LeVA1eTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE80eHF2ZVJIc3RvY0hvX1ktMUNreXdTdlEzMlI0RHBEUU9BQ0Jabk9BWWFDVENyQ2pweW1ZRlB3X3plYUJmcmh1T0dWY0U5YWZXQnhodV9XLTJrZUnSAWBBVV95cUxQSW1lYldpaWlZdV9XTTFxWVFhYnR2Um9ZSW52ZFdEZDk5N2JZblc0cXpjVnpVbFNSSTBtMTdNUzBqQm1tT2YteWJCaFI3NU0xQW82QUFjMXVSalhBb1pSSV8?oc=5</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1433,22 +1433,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>우회 선박 ‘통상 운임’ 관세 적용…전세사기 보증금 ‘3분의 1’ 국가가 보장 - v.daum.net</t>
+          <t>'韓관세 협상' 美상무장관, 엡스타인 관련 의회 조사 출석 - 뉴시스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>우회 선박 ‘통상 운임’ 관세 적용…전세사기 보증금 ‘3분의 1’ 국가가 보장&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>'韓관세 협상' 美상무장관, 엡스타인 관련 의회 조사 출석&amp;nbsp;&amp;nbsp;뉴시스</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 05:15:02 GMT</t>
+          <t>Wed, 06 May 2026 17:39:16 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5vOEMydUw5c0FxQU9zVkRhbDhkY0RNRTJPLVJXM19QU2V4aWc1OGhKRTZJMDZ1RzNuOFF5dFFFMGp3SHRqQW1reHVKMXhZWk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFAxYzhFSlMtek1jbXNsZWFTVzJ1VDcyWlBtQ1BfeEYyTTlucU9QamgzOXNydVQ3Q0NGdXIyc1YzLTBPc1BMX2M1VEIwNThFMGRxTkxRd2ppdWRRMGlPUkZBSdIBeEFVX3lxTE55VXFUYWpJV2xZaFpDZjA3a2xNTURudVk0QVR4OW9KdWZoS2ZoazlFbnE2RURfNUd4S3pJazNXVXd2QWRNcXdNdm1VMmZXM3U3SmlYTGRHM1llX0w0Q1dFWDZRWGdsX29QV1JIZklISllKWUxySkZBRA?oc=5</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1465,27 +1465,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>관세</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>무역협회, 美 투자행사서 “관세 불확실성 해소” 요구 - v.daum.net</t>
+          <t>[FTA 활용 성공 사례] H사-낚시용품 - 한국무역협회-KITA.NET</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>무역협회, 美 투자행사서 “관세 불확실성 해소” 요구&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>[FTA 활용 성공 사례] H사-낚시용품&amp;nbsp;&amp;nbsp;한국무역협회-KITA.NET</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 05:16:05 GMT</t>
+          <t>Wed, 06 May 2026 10:24:58 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBPaEZ6X2ZhN0dMUkNwNTM5aUhWWm5qNmxVYkhkUkRBWm1aWHB6REJjX2pheVFJVkhLa1ZlVk5Wd1E4WmpxcTJJQVd6Rnkyc2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNNlNpSkRTSUlKZEVEOENBOFFPaEd3X0ZMNGhObzJkbVFfWEJPZzJPTWd3SEpPeWRvNVRVX044MzJGRnY1S0RpelJzS2NiV29ZanhsRmF3V052c1hGUlBoZ3B5eTgzNXZJODNoOHQ0Q2I2b0tDRThpcHBJdzNyVGVhcmJscER6d1dJdFQ4Ng?oc=5</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1507,32 +1507,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[EU의 역습②]자동차 업계, FTA 혜택 지켰지만…현지화 압박 계속 - 연합인포맥스</t>
+          <t>'FTA 원산지관리 정보화 지원' 중소·중견기업 27개 선정 - 뉴시스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[EU의 역습②]자동차 업계, FTA 혜택 지켰지만…현지화 압박 계속&amp;nbsp;&amp;nbsp;연합인포맥스</t>
+          <t>'FTA 원산지관리 정보화 지원' 중소·중견기업 27개 선정&amp;nbsp;&amp;nbsp;뉴시스</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 01:13:14 GMT</t>
+          <t>Wed, 06 May 2026 21:00:00 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBtalc0TGNlSms4VU0tc0c2R2piM1VrbzM5N0N3RDNEanNsX1hUQmpsUEtpdnkyaFlYUHlPUzZDMzBTMUF4RUlNTXVVclRDV3pQbWdBNkxIUGtzdkNjRHpEZTZFYkI3bzRYenA2VlRvR20?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBzMzdPWjJzeUlMMEZjTjJTSWF1emZpdXQxN29DWUltTzRNcW9BYUs0aTNPeEQ4WExaWUZydUloS2hHWFBBUkRKbVBUNzgwT2NTUUdWMEkxTFNPNXBDbVdubNIBeEFVX3lxTE5VQUxnUmdWRmpJWk9yNVJvWFpVZkV4LUFtYTBfVzVwa013UFNmdm1jUUtqNXJiQ1dkLXlOVmdlY2JGRE5BSFR0RUFpZE56VHBPOWNWZmdBcUljaG1FSmwtaUtnVWlmZXRrY0p6b0F1MXpmN09yZ3Jndw?oc=5</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I30" t="inlineStr"/>
     </row>
@@ -1544,22 +1544,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FTA기금 과수고품질시설 현대화사업 추가 접수 - 뉴스N제주</t>
+          <t>[EU의 역습②]자동차 업계, FTA 혜택 지켰지만…현지화 압박 계속 - 연합인포맥스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FTA기금 과수고품질시설 현대화사업 추가 접수&amp;nbsp;&amp;nbsp;뉴스N제주</t>
+          <t>[EU의 역습②]자동차 업계, FTA 혜택 지켰지만…현지화 압박 계속&amp;nbsp;&amp;nbsp;연합인포맥스</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 12:41:13 GMT</t>
+          <t>Wed, 06 May 2026 01:13:14 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1Lc3c3T2JNMUhZSzdZc2RYcmV4alFUS0lhZ1lKY1E1THBIdzFtTWFuZnk2NjMyOTRRZXlOZkRJN3VQNWN5QVp4Wi1MTDZ3eVh4cFVSUGN4UkpvZzZ0eG56NHpXRUxNZk1sejd1Qw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBtalc0TGNlSms4VU0tc0c2R2piM1VrbzM5N0N3RDNEanNsX1hUQmpsUEtpdnkyaFlYUHlPUzZDMzBTMUF4RUlNTXVVclRDV3pQbWdBNkxIUGtzdkNjRHpEZTZFYkI3bzRYenA2VlRvR20?oc=5</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>대구FTA통상진흥센터, 원산지증명서 발급 교육 개최 - B world</t>
+          <t>FTA기금 과수고품질시설 현대화사업 추가 접수 - 뉴스N제주</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>대구FTA통상진흥센터, 원산지증명서 발급 교육 개최&amp;nbsp;&amp;nbsp;B world</t>
+          <t>FTA기금 과수고품질시설 현대화사업 추가 접수&amp;nbsp;&amp;nbsp;뉴스N제주</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 09:13:58 GMT</t>
+          <t>Wed, 06 May 2026 12:41:13 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFA1emlOeVgxZEJlT2g3bF9OR3dGaUlmT25NbXJEbUs5bHROQ21vNXBoV0FPdVluQzNubGV5bWRmTGxFQzdfUXFxdmVzLS1mSzJhN1pPTkU4d1BxTHduLWd3REtiUFYycVlyemEyLS0zU1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1Lc3c3T2JNMUhZSzdZc2RYcmV4alFUS0lhZ1lKY1E1THBIdzFtTWFuZnk2NjMyOTRRZXlOZkRJN3VQNWN5QVp4Wi1MTDZ3eVh4cFVSUGN4UkpvZzZ0eG56NHpXRUxNZk1sejd1Qw?oc=5</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I32" t="inlineStr"/>
     </row>
@@ -1618,32 +1618,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[공지] 3/10, 3/14 한미FTA 폐기 범국민 촛불대회 - 참여연대</t>
+          <t>대구FTA통상진흥센터, 원산지증명서 발급 교육 개최 - B world</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[공지] 3/10, 3/14 한미FTA 폐기 범국민 촛불대회&amp;nbsp;&amp;nbsp;참여연대</t>
+          <t>대구FTA통상진흥센터, 원산지증명서 발급 교육 개최&amp;nbsp;&amp;nbsp;B world</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 05 May 2026 22:11:42 GMT</t>
+          <t>Wed, 06 May 2026 09:13:58 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1oNHNrbDZ2dE5GUTFuUmdYN0dsbDV2X0dpajAtV2VmOGk5MEVfclVOem0wRlRNUlVPelRpcnNzaE1BS2phcG90bTVvYUltS1dZZmNOMGF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFA1emlOeVgxZEJlT2g3bF9OR3dGaUlmT25NbXJEbUs5bHROQ21vNXBoV0FPdVluQzNubGV5bWRmTGxFQzdfUXFxdmVzLS1mSzJhN1pPTkU4d1BxTHduLWd3REtiUFYycVlyemEyLS0zU1k?oc=5</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I33" t="inlineStr"/>
     </row>
@@ -1655,59 +1655,59 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>서귀포시, 2026년 FTA기금 과수 고품질시설 현대화사업 추가 신청·접수 - hkilbo.kr</t>
+          <t>산업부, FTA 원산지 관리 정보화 지원 기업 27개 선정 - 네이트</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>서귀포시, 2026년 FTA기금 과수 고품질시설 현대화사업 추가 신청·접수&amp;nbsp;&amp;nbsp;hkilbo.kr</t>
+          <t>산업부, FTA 원산지 관리 정보화 지원 기업 27개 선정&amp;nbsp;&amp;nbsp;네이트</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 07:54:20 GMT</t>
+          <t>Wed, 06 May 2026 21:01:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9XSkZTX2J2NlRZMHo2X1oyVU1FLWUzcVhqNDUtcVRiTEhPUEpYcDRvSG1Lc1hFY05GV2pleEFoVGx1LVplZVhUUS0xakoya2dac0JybDM2bVR3UG1QNGJQdUtSZE9ObGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1iczlna3JKcWdSTTdEbUM5dlpDdlBTRlpidThGdFBpMUR4bDN3aDluWTJIV0V3Wnd5Vmwxa0pDYWVKQmN6bDU2UzYwWUdSeS1kVy0w?oc=5</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>“돈 내고도 모르는 내 밥상”···고도화된 배달앱 속 원산지 표시 ‘사각지대’ - 이뉴스투데이</t>
+          <t>서귀포시, 2026년 FTA기금 과수 고품질시설 현대화사업 추가 신청·접수 - hkilbo.kr</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>“돈 내고도 모르는 내 밥상”···고도화된 배달앱 속 원산지 표시 ‘사각지대’&amp;nbsp;&amp;nbsp;이뉴스투데이</t>
+          <t>서귀포시, 2026년 FTA기금 과수 고품질시설 현대화사업 추가 신청·접수&amp;nbsp;&amp;nbsp;hkilbo.kr</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 09:00:00 GMT</t>
+          <t>Wed, 06 May 2026 07:54:20 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1yMXBQOXBvWmV6QUZ6ZHhlbTFRZllySzhJdEFsWEp6MWdFWi1BZG1IbE1QV1RpX1JZREVxREpybUJ0VHJDZ3FjTVduQVkwUVl6WmhkUFBTMmp6b2F5ZWM0ei05VVdhTVhyT1AzZldWb1pfQdIBdEFVX3lxTE9HMlhkN0JzOWxMaHJGN3lERTdURC1DSzdmcXh3VkVmek55UEZxOGltT0hYYUlYaE5JR2JSUmpQS1lva0tPNDhvUFVQVGN0VHhpM2JHbktReF9EdmVqNkhhazdEOVUzQnZ0RDVVQzhHVDIzNnRo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9XSkZTX2J2NlRZMHo2X1oyVU1FLWUzcVhqNDUtcVRiTEhPUEpYcDRvSG1Lc1hFY05GV2pleEFoVGx1LVplZVhUUS0xakoya2dac0JybDM2bVR3UG1QNGJQdUtSZE9ObGc?oc=5</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1729,22 +1729,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>경남농관원, 화훼류 원산지 단속 실시…‘카네이션·국화 집중 점검’ - 농수축산신문</t>
+          <t>수출기업 원산지 관리 디지털화…산업부, 27개사 컨설팅 지원 - v.daum.net</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>경남농관원, 화훼류 원산지 단속 실시…‘카네이션·국화 집중 점검’&amp;nbsp;&amp;nbsp;농수축산신문</t>
+          <t>수출기업 원산지 관리 디지털화…산업부, 27개사 컨설팅 지원&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 02:02:06 GMT</t>
+          <t>Wed, 06 May 2026 21:01:24 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1UZjdyUmIxQ0RaSEJfS1lHZERyTEtTazJhbG5WdG9OeE5rN3N1aEZhbnI2OUgxWTZZSk03YnV3N3JEYW5ST2psdDRGMTl0Yk1OOFhDMDBkTm55MDRsR2RfNTJsR1g0NnRZYjd4Mg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBRcGh5TVdOaTJIQXFJUzdpNE5IOGRyY3F6cHBpZk8tSWdRTUxFajNYZEVLa2E0ZW9LUk91SHlLaTRHNnlvQWhXQWc3WTk1TUk?oc=5</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1766,22 +1766,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>수출 9천억 돌파한 ‘K-김’…관세청, 통관·원산지 지원 강화 - 해양레저신문</t>
+          <t>산업부, FTA 원산지 관리 정보화 지원 기업 27개 선정 - v.daum.net</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>수출 9천억 돌파한 ‘K-김’…관세청, 통관·원산지 지원 강화&amp;nbsp;&amp;nbsp;해양레저신문</t>
+          <t>산업부, FTA 원산지 관리 정보화 지원 기업 27개 선정&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 00:49:00 GMT</t>
+          <t>Wed, 06 May 2026 21:02:08 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5NZmpWRzlmYXk2cGdrU3JGUlFsVU1UT2hPR0VGRWp2a1dyRzZmM01MbU1ONGVFNmZzREZZRThjM1ZPUTVIUmlYMmhCNHRLZjlnZFFqWGdPR0ZMbDdG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9YUW9aenpwaHJYLUh2c2V6YVBocDk3QVIzd2JQTDBiNUFlOGk1cWxka3M1TEpRd3oxdTRWUy1UaktjMnptSlFHMkI4R1FuYkU?oc=5</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I37" t="inlineStr"/>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[기고] 대체보양식? 소비자는 흑염소의 원산지가 궁금하다 - 아시아투데이</t>
+          <t>"美 관세 환급 서둘러야"…원산지 오류 땐 추징·과징금 역풍 주의 - 뉴스1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[기고] 대체보양식? 소비자는 흑염소의 원산지가 궁금하다&amp;nbsp;&amp;nbsp;아시아투데이</t>
+          <t>"美 관세 환급 서둘러야"…원산지 오류 땐 추징·과징금 역풍 주의&amp;nbsp;&amp;nbsp;뉴스1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 08:38:36 GMT</t>
+          <t>Wed, 06 May 2026 06:44:47 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE41bDJzRjJtMkJXU0xLbFkyM3lUb1R0V1dYaTQ2Z1I1anFLSEw3UlF4OFVORVVSa010c2xJelBUQ2lVcmYyb0hpemU5dHB2SUtEMXA5Mk5pVGhyb3p6UVdiNVJjckRWYzBSWERaVTRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBzUnRKY1J5NmRkT05WYnVPa0RxU1BPSmFRYURqVU1pSHgtUC1JVFFqbmpuQ3o1cHJjeWRCRW8yRG12c0FFWTllZjctXzFkZkUyWmFYZnhOTl9QbzhpdExuQm9oX1I?oc=5</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I38" t="inlineStr"/>
     </row>
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>소비자들은 상품의 원산지를 추적할 수 있는 모바일 애플리케이션을 갖게 될 것입니다. - Vietnam.vn</t>
+          <t>“돈 내고도 모르는 내 밥상”···고도화된 배달앱 속 원산지 표시 ‘사각지대’ - 이뉴스투데이</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>소비자들은 상품의 원산지를 추적할 수 있는 모바일 애플리케이션을 갖게 될 것입니다.&amp;nbsp;&amp;nbsp;Vietnam.vn</t>
+          <t>“돈 내고도 모르는 내 밥상”···고도화된 배달앱 속 원산지 표시 ‘사각지대’&amp;nbsp;&amp;nbsp;이뉴스투데이</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 03:25:42 GMT</t>
+          <t>Wed, 06 May 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQMHYxa2YxVktKeWJRZ3plV3dCUEZfQ3ViZi1aUkN1Y1owS3VyMXpQVDNoNW1uV2dFemdtaXhfc1NJV09RNndsMUpTbHhWRGplckFxWUd4R3JWSnB6X3ZtYWFiNVFRbXFSb1pYMUFpdmpJNGtGM2pYU0pra1BxckZsbTA5SHdtdW9mNU9IRVV5Q01mOTdK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1yMXBQOXBvWmV6QUZ6ZHhlbTFRZllySzhJdEFsWEp6MWdFWi1BZG1IbE1QV1RpX1JZREVxREpybUJ0VHJDZ3FjTVduQVkwUVl6WmhkUFBTMmp6b2F5ZWM0ei05VVdhTVhyT1AzZldWb1pfQdIBdEFVX3lxTE9HMlhkN0JzOWxMaHJGN3lERTdURC1DSzdmcXh3VkVmek55UEZxOGltT0hYYUlYaE5JR2JSUmpQS1lva0tPNDhvUFVQVGN0VHhpM2JHbktReF9EdmVqNkhhazdEOVUzQnZ0RDVVQzhHVDIzNnRo?oc=5</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I39" t="inlineStr"/>
     </row>
@@ -1877,22 +1877,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>농관원 경북지원, 가정의달 맞아 화훼 원산지 단속 - 뉴스1</t>
+          <t>[기고] 대체보양식? 소비자는 흑염소의 원산지가 궁금하다 - 아시아투데이</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>농관원 경북지원, 가정의달 맞아 화훼 원산지 단속&amp;nbsp;&amp;nbsp;뉴스1</t>
+          <t>[기고] 대체보양식? 소비자는 흑염소의 원산지가 궁금하다&amp;nbsp;&amp;nbsp;아시아투데이</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 02:36:36 GMT</t>
+          <t>Wed, 06 May 2026 08:38:36 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9aX3ljT0Y0c3ItSEMtRDNfUDlCVl9kS0tiaExiVzN5MXh6RHhScWZ2bm5wRkg4dFM1NG54NjgyUjZyWjRUdlNUemUybjZFUWpVbkxRVXZEdHBsX3dJLXVZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE41bDJzRjJtMkJXU0xLbFkyM3lUb1R0V1dYaTQ2Z1I1anFLSEw3UlF4OFVORVVSa010c2xJelBUQ2lVcmYyb0hpemU5dHB2SUtEMXA5Mk5pVGhyb3p6UVdiNVJjckRWYzBSWERaVTRB?oc=5</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1914,96 +1914,96 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>농관원 경북지원, 가정의달 맞아 화훼 원산지 단속 - 네이트</t>
+          <t>산업부, FTA 원산지 관리 정보화 지원 기업 27개 선정 - 연합뉴스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>농관원 경북지원, 가정의달 맞아 화훼 원산지 단속&amp;nbsp;&amp;nbsp;네이트</t>
+          <t>산업부, FTA 원산지 관리 정보화 지원 기업 27개 선정&amp;nbsp;&amp;nbsp;연합뉴스</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 02:37:00 GMT</t>
+          <t>Wed, 06 May 2026 21:00:03 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE55NU5lMWhpemEybFYwbUtQZFpMTzRkbEYya3pvNFVNTjllNjk3RFhRQU1yck1iWUQ5Nl9NOGh2dTRnZElBbVdUeE83UjBDeXBVNHpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE55S3lmdUg5d05MTXktdU9kZFBqTE5KT05ZcmswTDN4aUNMS0JYcXlLbE5BanJnVWZmUldXWGZwd1pkX0pGNnR6Qll0TnRyRUJKdlE5bTJJVE9PcmlmZkJ0NtIBYEFVX3lxTE55S3lmdUg5d05MTXktdU9kZFBqTE5KT05ZcmswTDN4aUNMS0JYcXlLbE5BanJnVWZmUldXWGZwd1pkX0pGNnR6Qll0TnRyRUJKdlE5bTJJVE9PcmlmZkJ0Ng?oc=5</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>원산지</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>美, 대중국 반도체장비 수출통제…中 "자립만 가속" - v.daum.net</t>
+          <t>'FTA 원산지관리 정보화 지원' 중소·중견기업 27개 선정 - 뉴시스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>美, 대중국 반도체장비 수출통제…中 "자립만 가속"&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>'FTA 원산지관리 정보화 지원' 중소·중견기업 27개 선정&amp;nbsp;&amp;nbsp;뉴시스</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 09:27:01 GMT</t>
+          <t>Wed, 06 May 2026 21:00:00 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9TUHZKVVN5ZUxzcXpOendpNjlYTUc3VTBDWmtBUU5oaG1EZ1RxcC1NTHhnMHdQY08yS3FRakNZeThKc2dpU0N5RkJFalVsWU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5VQUxnUmdWRmpJWk9yNVJvWFpVZkV4LUFtYTBfVzVwa013UFNmdm1jUUtqNXJiQ1dkLXlOVmdlY2JGRE5BSFR0RUFpZE56VHBPOWNWZmdBcUljaG1FSmwtaUtnVWlmZXRrY0p6b0F1MXpmN09yZ3Jnd9IBeEFVX3lxTE5VQUxnUmdWRmpJWk9yNVJvWFpVZkV4LUFtYTBfVzVwa013UFNmdm1jUUtqNXJiQ1dkLXlOVmdlY2JGRE5BSFR0RUFpZE56VHBPOWNWZmdBcUljaG1FSmwtaUtnVWlmZXRrY0p6b0F1MXpmN09yZ3Jndw?oc=5</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>원산지</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>美, 대중국 반도체장비 수출통제 강화에…中 "자립만 가속할뿐" - 연합뉴스</t>
+          <t>수출기업 원산지 관리 디지털화…산업부, 27개사 컨설팅 지원 - 뉴스1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>美, 대중국 반도체장비 수출통제 강화에…中 "자립만 가속할뿐"&amp;nbsp;&amp;nbsp;연합뉴스</t>
+          <t>수출기업 원산지 관리 디지털화…산업부, 27개사 컨설팅 지원&amp;nbsp;&amp;nbsp;뉴스1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 08:44:01 GMT</t>
+          <t>Wed, 06 May 2026 21:00:00 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1McjVqaGRXdC1Bd0FabTVKclZnRXdYQUpVTkRBTVpIRkZuMG9hUkxCSVhmRXA4UWdMdjRvNWQ4OW9ucWtBNnotWnlhU0haX2VYd0JWNy1Tc084djjSAWBBVV95cUxPMGZEN2dfTFUzNjVHNXJHME5QRVJWWkZ4VjJHN09HRWwzRDFwVk84NDEtenZpeTFpd2xoZzVvQWoxdEZ4UmJMR3ZKaE9peWoxSHR2ckZUS1N1RjBrd0x3RVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1FODNMNHlFSnF6RjMyWGo3SEQxdXJiUWNtM3VKdUtBWk1FVmxoeWxZY2JVMTRxTmhoR3RWLWtWeE5DdTkwbjdTandIbkN3TkJkcGw3aDhhYXZrblEzYWFR?oc=5</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2013,34 +2013,34 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>원산지</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>전장 바꾼 우크라 드론, 약점은 中부품…대만으로 눈 돌렸다 - 뉴시스</t>
+          <t>경남농관원, 화훼류 원산지 단속 실시…‘카네이션·국화 집중 점검’ - 농수축산신문</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>전장 바꾼 우크라 드론, 약점은 中부품…대만으로 눈 돌렸다&amp;nbsp;&amp;nbsp;뉴시스</t>
+          <t>경남농관원, 화훼류 원산지 단속 실시…‘카네이션·국화 집중 점검’&amp;nbsp;&amp;nbsp;농수축산신문</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 05:54:55 GMT</t>
+          <t>Wed, 06 May 2026 02:02:06 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9nblNuRkRUeDFMaDBoSjFmMWptbEdYaXlzUE9jdnhuYmlJRmxEVk1oTGxlNk9FM3N4UWswcm1vWEJWdWxNR1VXOTgwMlo0NEg5RWJYOVFoLTVIOE13NFV3dNIBeEFVX3lxTE5kZGFyX0VkeDJvY1pYTGdyOURBalRWa3pDM3NoNW12NExpS0k0bXRQelU2VG5JcWNkXzlVUDVjQVBCZ19wSHhPWHdxMkV4SncyemU5cUNRaUYxTjVKZVQwUmtscmE2NW50Wm15Z01EekVHb2pHakpfMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1UZjdyUmIxQ0RaSEJfS1lHZERyTEtTazJhbG5WdG9OeE5rN3N1aEZhbnI2OUgxWTZZSk03YnV3N3JEYW5ST2psdDRGMTl0Yk1OOFhDMDBkTm55MDRsR2RfNTJsR1g0NnRZYjd4Mg?oc=5</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2050,34 +2050,34 @@
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>원산지</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>日, 필리핀에 중고 호위함 수출 추진…韓 방산과 경쟁 가능성 - 아주경제</t>
+          <t>농관원 경북지원, 가정의달 맞아 화훼 원산지 단속 - 뉴스1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>日, 필리핀에 중고 호위함 수출 추진…韓 방산과 경쟁 가능성&amp;nbsp;&amp;nbsp;아주경제</t>
+          <t>농관원 경북지원, 가정의달 맞아 화훼 원산지 단속&amp;nbsp;&amp;nbsp;뉴스1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 07:55:22 GMT</t>
+          <t>Wed, 06 May 2026 02:36:36 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5uX0pHQ0Z2WW0xMEJKdHRHQ1h4TE5saXdTLU9iZlZhS1hNYlZVN1BacmhuNXFpb25FSGtJdzlWSjVBVURJZE9Dd2d3cUMyNXNqRnhPMk4tcGNYUdIBWEFVX3lxTFBqaXIzOVF6QnUwNmExWjZFbUZpM1IyRzRTQ19mQWVGRVdwM0R4MVk5TmFfSUlpWkN2bm15V3ZBSTdkSGsweGpRVEVOcDVaVl9WSFA1NUwtX3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9aX3ljT0Y0c3ItSEMtRDNfUDlCVl9kS0tiaExiVzN5MXh6RHhScWZ2bm5wRkg4dFM1NG54NjgyUjZyWjRUdlNUemUybjZFUWpVbkxRVXZEdHBsX3dJLXVZ?oc=5</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2087,44 +2087,44 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>원산지</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>美 제재 무시하는 中업체들…이란·러 드론 부품 공급에 홍보까지 - 뉴시스</t>
+          <t>수출 9천억 돌파한 ‘K-김’…관세청, 통관·원산지 지원 강화 - 해양레저신문</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>美 제재 무시하는 中업체들…이란·러 드론 부품 공급에 홍보까지&amp;nbsp;&amp;nbsp;뉴시스</t>
+          <t>수출 9천억 돌파한 ‘K-김’…관세청, 통관·원산지 지원 강화&amp;nbsp;&amp;nbsp;해양레저신문</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 08:31:56 GMT</t>
+          <t>Wed, 06 May 2026 00:49:00 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBkQnZILUhZaTNnSXQzcURmamNpWTI4cEVjQm9adTBlUklkelVERi1neHV2QlI5UXJnUmZpbWRENHhHaGFMd3h5VGdoOHBHN3JjSFJQS0hvWGxKYy1zc2hYOdIBeEFVX3lxTE1VNkVER05QQy0wTGtqRHZGekdOVFQxMzFTekM4cF9fR2hxemtEZmdjbzJaclhXTGdCUTZfRDMzak11R0ZGNkh5VmJPWmZCVWQ5cm84UkdkNzZfOV9pWEpfYTI0dkgxc0JUeWdtSEVSU3RhTzlZY3YwOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5NZmpWRzlmYXk2cGdrU3JGUlFsVU1UT2hPR0VGRWp2a1dyRzZmM01MbU1ONGVFNmZzREZZRThjM1ZPUTVIUmlYMmhCNHRLZjlnZFFqWGdPR0ZMbDdG?oc=5</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I46" t="inlineStr"/>
     </row>
@@ -2136,22 +2136,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>일본 무기수출 가속…필리핀과 실무협의 틀 구성 합의 - 네이트</t>
+          <t>美, 대중국 반도체장비 수출통제…中 "자립만 가속" - v.daum.net</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>일본 무기수출 가속…필리핀과 실무협의 틀 구성 합의&amp;nbsp;&amp;nbsp;네이트</t>
+          <t>美, 대중국 반도체장비 수출통제…中 "자립만 가속"&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 02:39:00 GMT</t>
+          <t>Wed, 06 May 2026 09:27:01 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1iSTFGX3BDaDZJb1NUTGR6LWM2NUhzdmt4X3B6ajlJcDd1aDZReURIdHpXa1Azbkp2QWVmNnVreTZoODhNaGwzQ25XaUprOXBtenY4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9TUHZKVVN5ZUxzcXpOendpNjlYTUc3VTBDWmtBUU5oaG1EZ1RxcC1NTHhnMHdQY08yS3FRakNZeThKc2dpU0N5RkJFalVsWU0?oc=5</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" t="inlineStr"/>
     </row>
@@ -2173,22 +2173,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>日 무기수출 가속…필리핀과 실무 협의 틀 구성에 합의 - 네이트</t>
+          <t>중국, 해외 제재 대응 규정 즉시 발효…한국 기업, 공급망 재편 불가피 - 브랜드경제신문</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>日 무기수출 가속…필리핀과 실무 협의 틀 구성에 합의&amp;nbsp;&amp;nbsp;네이트</t>
+          <t>중국, 해외 제재 대응 규정 즉시 발효…한국 기업, 공급망 재편 불가피&amp;nbsp;&amp;nbsp;브랜드경제신문</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wed, 06 May 2026 02:00:00 GMT</t>
+          <t>Wed, 06 May 2026 22:09:37 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1pNTc5YUVIeGljOGwyUHNEb015Y0M4MU9NZFBPUWpGSm1OMlRSNTVQZXlFckZGc1g4cmwzRDdFWUUzcC0ydEJldEM0dGlDU1d0Qk93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTEFVX3lxTE13Vm5nSXNPeEpWNHM0ZTVla3VWZzFKMU5nT243T2x1UkJqenhiUXRSc0tVeHlFZHkxUWc2cU96dmFDZ0VZajBtWFFUb3k?oc=5</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2198,9 +2198,157 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
+        <v>5</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>美, 대중국 반도체장비 수출통제 강화에…中 "자립만 가속할뿐" - 네이트</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>美, 대중국 반도체장비 수출통제 강화에…中 "자립만 가속할뿐"&amp;nbsp;&amp;nbsp;네이트</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 08:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9odzBHOHhaUWZ6cWc5MkVCRmh1aGwtVzNCc0xZM1R1LWUxV0hSM0FsbmRPenpLd2RqNTVRRTZmdEhOQ3h0N1dnNmV5ekl3NjhDY2p3?oc=5</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>전장 바꾼 우크라 드론, 약점은 中부품…대만으로 눈 돌렸다 - 뉴시스</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>전장 바꾼 우크라 드론, 약점은 中부품…대만으로 눈 돌렸다&amp;nbsp;&amp;nbsp;뉴시스</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 05:54:55 GMT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9nblNuRkRUeDFMaDBoSjFmMWptbEdYaXlzUE9jdnhuYmlJRmxEVk1oTGxlNk9FM3N4UWswcm1vWEJWdWxNR1VXOTgwMlo0NEg5RWJYOVFoLTVIOE13NFV3dNIBeEFVX3lxTE5kZGFyX0VkeDJvY1pYTGdyOURBalRWa3pDM3NoNW12NExpS0k0bXRQelU2VG5JcWNkXzlVUDVjQVBCZ19wSHhPWHdxMkV4SncyemU5cUNRaUYxTjVKZVQwUmtscmE2NW50Wm15Z01EekVHb2pHakpfMw?oc=5</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
         <v>1</v>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>美 제재 무시하는 中업체들…이란·러 드론 부품 공급에 홍보까지 - 뉴시스</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>美 제재 무시하는 中업체들…이란·러 드론 부품 공급에 홍보까지&amp;nbsp;&amp;nbsp;뉴시스</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 08:31:56 GMT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBkQnZILUhZaTNnSXQzcURmamNpWTI4cEVjQm9adTBlUklkelVERi1neHV2QlI5UXJnUmZpbWRENHhHaGFMd3h5VGdoOHBHN3JjSFJQS0hvWGxKYy1zc2hYOdIBeEFVX3lxTE1VNkVER05QQy0wTGtqRHZGekdOVFQxMzFTekM4cF9fR2hxemtEZmdjbzJaclhXTGdCUTZfRDMzak11R0ZGNkh5VmJPWmZCVWQ5cm84UkdkNzZfOV9pWEpfYTI0dkgxc0JUeWdtSEVSU3RhTzlZY3YwOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>日, 필리핀에 중고 호위함 수출 추진…韓 방산과 경쟁 가능성 - 아주경제</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>日, 필리핀에 중고 호위함 수출 추진…韓 방산과 경쟁 가능성&amp;nbsp;&amp;nbsp;아주경제</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 07:55:22 GMT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5uX0pHQ0Z2WW0xMEJKdHRHQ1h4TE5saXdTLU9iZlZhS1hNYlZVN1BacmhuNXFpb25FSGtJdzlWSjVBVURJZE9Dd2d3cUMyNXNqRnhPMk4tcGNYUdIBWEFVX3lxTFBqaXIzOVF6QnUwNmExWjZFbUZpM1IyRzRTQ19mQWVGRVdwM0R4MVk5TmFfSUlpWkN2bm15V3ZBSTdkSGsweGpRVEVOcDVaVl9WSFA1NUwtX3M?oc=5</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
